--- a/ЛР2-3_Объем_рынка/Excel/ЦВ_цифровая_воронка_NotaCode.xlsx
+++ b/ЛР2-3_Объем_рынка/Excel/ЦВ_цифровая_воронка_NotaCode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ИИТ\ЭлектронныйБизнес\ЛР2-3_Объем_рынка\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ИИТ\ЭлектронныйБизнес\ЛР2-3_Объем_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413DBDEB-1617-4124-B69B-8200606E0905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56B6A74-A318-4A48-8349-DB0D387EC586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="3975" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Методика" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,20 @@
     <sheet name="09_Источники" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029" refMode="R1C1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1722,7 +1736,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="5" width="20" customWidth="1"/>
@@ -1731,7 +1745,7 @@
     <col min="8" max="10" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18">
+    <row r="1" spans="1:10" ht="17.649999999999999">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1757,7 +1771,7 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="30">
+    <row r="3" spans="1:10" ht="27.75">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1785,7 +1799,7 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="114">
+    <row r="4" spans="1:10" ht="108">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -1825,7 +1839,7 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="15">
+    <row r="6" spans="1:10" ht="13.9">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -1845,7 +1859,7 @@
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10" ht="71.25">
+    <row r="7" spans="1:10" ht="67.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -1865,7 +1879,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="42.75">
+    <row r="8" spans="1:10" ht="40.5">
       <c r="A8" s="1">
         <v>2</v>
       </c>
@@ -1885,7 +1899,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" ht="71.25">
+    <row r="9" spans="1:10" ht="54">
       <c r="A9" s="1">
         <v>3</v>
       </c>
@@ -1905,7 +1919,7 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:10" ht="42.75">
+    <row r="10" spans="1:10" ht="40.5">
       <c r="A10" s="1">
         <v>4</v>
       </c>
@@ -1925,7 +1939,7 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:10" ht="57">
+    <row r="11" spans="1:10" ht="54">
       <c r="A11" s="1">
         <v>5</v>
       </c>
@@ -1945,7 +1959,7 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:10" ht="42.75">
+    <row r="12" spans="1:10" ht="40.5">
       <c r="A12" s="1">
         <v>6</v>
       </c>
@@ -1965,7 +1979,7 @@
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:10" ht="85.5">
+    <row r="13" spans="1:10" ht="81">
       <c r="A13" s="1">
         <v>7</v>
       </c>
@@ -1985,7 +1999,7 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:10" ht="57">
+    <row r="14" spans="1:10" ht="54">
       <c r="A14" s="1">
         <v>8</v>
       </c>
@@ -2017,7 +2031,7 @@
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:10" ht="15">
+    <row r="16" spans="1:10" ht="13.9">
       <c r="A16" s="2" t="s">
         <v>45</v>
       </c>
@@ -2037,7 +2051,7 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" ht="28.5">
+    <row r="17" spans="1:10" ht="27">
       <c r="A17" s="4" t="s">
         <v>49</v>
       </c>
@@ -2077,7 +2091,7 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" ht="42.75">
+    <row r="19" spans="1:10" ht="40.5">
       <c r="A19" s="3" t="s">
         <v>57</v>
       </c>
@@ -2360,7 +2374,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="5" width="20" customWidth="1"/>
@@ -2369,7 +2383,7 @@
     <col min="8" max="10" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18">
+    <row r="1" spans="1:10" ht="17.649999999999999">
       <c r="A1" s="17" t="s">
         <v>248</v>
       </c>
@@ -2395,7 +2409,7 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="30">
+    <row r="3" spans="1:10" ht="27.75">
       <c r="A3" s="2" t="s">
         <v>249</v>
       </c>
@@ -2419,7 +2433,7 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="42.75">
+    <row r="4" spans="1:10" ht="40.5">
       <c r="A4" s="1" t="s">
         <v>254</v>
       </c>
@@ -2430,7 +2444,7 @@
         <v>306</v>
       </c>
       <c r="D4" s="16">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>256</v>
@@ -2443,7 +2457,7 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="42.75">
+    <row r="5" spans="1:10" ht="40.5">
       <c r="A5" s="1" t="s">
         <v>258</v>
       </c>
@@ -2454,7 +2468,7 @@
         <v>313</v>
       </c>
       <c r="D5" s="16">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>256</v>
@@ -2467,7 +2481,7 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="42.75">
+    <row r="6" spans="1:10" ht="40.5">
       <c r="A6" s="1" t="s">
         <v>261</v>
       </c>
@@ -2478,7 +2492,7 @@
         <v>263</v>
       </c>
       <c r="D6" s="16">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>121</v>
@@ -2491,7 +2505,7 @@
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10" ht="42.75">
+    <row r="7" spans="1:10" ht="40.5">
       <c r="A7" s="1" t="s">
         <v>265</v>
       </c>
@@ -2502,7 +2516,7 @@
         <v>267</v>
       </c>
       <c r="D7" s="16">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>121</v>
@@ -2515,7 +2529,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="114">
+    <row r="8" spans="1:10" ht="108">
       <c r="A8" s="1" t="s">
         <v>269</v>
       </c>
@@ -2526,7 +2540,7 @@
         <v>315</v>
       </c>
       <c r="D8" s="16">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>121</v>
@@ -2539,7 +2553,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" ht="42.75">
+    <row r="9" spans="1:10" ht="40.5">
       <c r="A9" s="1" t="s">
         <v>272</v>
       </c>
@@ -2550,7 +2564,7 @@
         <v>307</v>
       </c>
       <c r="D9" s="8">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>121</v>
@@ -2563,7 +2577,7 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:10" ht="85.5">
+    <row r="10" spans="1:10" ht="81">
       <c r="A10" s="1" t="s">
         <v>275</v>
       </c>
@@ -2574,7 +2588,7 @@
         <v>308</v>
       </c>
       <c r="D10" s="8">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>121</v>
@@ -2966,7 +2980,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="5" width="20" customWidth="1"/>
@@ -2975,7 +2989,7 @@
     <col min="8" max="10" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18">
+    <row r="1" spans="1:10" ht="17.649999999999999">
       <c r="A1" s="17" t="s">
         <v>60</v>
       </c>
@@ -3001,7 +3015,7 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="30">
+    <row r="3" spans="1:10" ht="27.75">
       <c r="A3" s="2" t="s">
         <v>61</v>
       </c>
@@ -3025,7 +3039,7 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="99.75">
+    <row r="4" spans="1:10" ht="81">
       <c r="A4" s="1" t="s">
         <v>65</v>
       </c>
@@ -3049,7 +3063,7 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="42.75">
+    <row r="5" spans="1:10" ht="40.5">
       <c r="A5" s="1" t="s">
         <v>70</v>
       </c>
@@ -3073,7 +3087,7 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="42.75">
+    <row r="6" spans="1:10" ht="40.5">
       <c r="A6" s="1" t="s">
         <v>75</v>
       </c>
@@ -3097,7 +3111,7 @@
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10" ht="28.5">
+    <row r="7" spans="1:10" ht="27">
       <c r="A7" s="1" t="s">
         <v>80</v>
       </c>
@@ -3121,7 +3135,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="99.75">
+    <row r="8" spans="1:10" ht="94.5">
       <c r="A8" s="1" t="s">
         <v>84</v>
       </c>
@@ -3145,7 +3159,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" ht="57">
+    <row r="9" spans="1:10" ht="40.5">
       <c r="A9" s="1" t="s">
         <v>88</v>
       </c>
@@ -3169,7 +3183,7 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:10" ht="57">
+    <row r="10" spans="1:10" ht="54">
       <c r="A10" s="1" t="s">
         <v>90</v>
       </c>
@@ -3193,7 +3207,7 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:10" ht="71.25">
+    <row r="11" spans="1:10" ht="67.5">
       <c r="A11" s="1" t="s">
         <v>92</v>
       </c>
@@ -3217,7 +3231,7 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:10" ht="171">
+    <row r="12" spans="1:10" ht="162">
       <c r="A12" s="1" t="s">
         <v>94</v>
       </c>
@@ -3241,7 +3255,7 @@
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:10" ht="114">
+    <row r="13" spans="1:10" ht="108">
       <c r="A13" s="1" t="s">
         <v>97</v>
       </c>
@@ -3265,12 +3279,12 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:10" ht="42.75">
+    <row r="14" spans="1:10" ht="27">
       <c r="A14" s="1" t="s">
         <v>99</v>
       </c>
       <c r="B14" s="8">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>100</v>
@@ -3301,7 +3315,7 @@
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:10" ht="45">
+    <row r="16" spans="1:10" ht="27.75">
       <c r="A16" s="2" t="s">
         <v>102</v>
       </c>
@@ -3663,7 +3677,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="5" width="20" customWidth="1"/>
@@ -3672,7 +3686,7 @@
     <col min="8" max="10" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18">
+    <row r="1" spans="1:10" ht="17.649999999999999">
       <c r="A1" s="17" t="s">
         <v>111</v>
       </c>
@@ -3698,7 +3712,7 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="30">
+    <row r="3" spans="1:10" ht="27.75">
       <c r="A3" s="2" t="s">
         <v>112</v>
       </c>
@@ -3728,7 +3742,7 @@
       </c>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="85.5">
+    <row r="4" spans="1:10" ht="81">
       <c r="A4" s="1" t="s">
         <v>120</v>
       </c>
@@ -3760,7 +3774,7 @@
       </c>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="85.5">
+    <row r="5" spans="1:10" ht="67.5">
       <c r="A5" s="1" t="s">
         <v>122</v>
       </c>
@@ -3792,7 +3806,7 @@
       </c>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="57">
+    <row r="6" spans="1:10" ht="54">
       <c r="A6" s="1" t="s">
         <v>124</v>
       </c>
@@ -3824,7 +3838,7 @@
       </c>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10" ht="42.75">
+    <row r="7" spans="1:10" ht="40.5">
       <c r="A7" s="1" t="s">
         <v>126</v>
       </c>
@@ -3856,7 +3870,7 @@
       </c>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="42.75">
+    <row r="8" spans="1:10" ht="40.5">
       <c r="A8" s="1" t="s">
         <v>128</v>
       </c>
@@ -3888,7 +3902,7 @@
       </c>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" ht="42.75">
+    <row r="9" spans="1:10" ht="40.5">
       <c r="A9" s="1" t="s">
         <v>130</v>
       </c>
@@ -3964,7 +3978,7 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:10" ht="15">
+    <row r="12" spans="1:10" ht="13.9">
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
@@ -3988,7 +4002,7 @@
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:10" ht="42.75">
+    <row r="13" spans="1:10" ht="40.5">
       <c r="A13" s="1" t="s">
         <v>136</v>
       </c>
@@ -4013,7 +4027,7 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:10" ht="28.5">
+    <row r="14" spans="1:10" ht="27">
       <c r="A14" s="1" t="s">
         <v>141</v>
       </c>
@@ -4038,7 +4052,7 @@
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:10" ht="28.5">
+    <row r="15" spans="1:10" ht="27">
       <c r="A15" s="1" t="s">
         <v>144</v>
       </c>
@@ -4382,7 +4396,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="5" width="20" customWidth="1"/>
@@ -4391,7 +4405,7 @@
     <col min="8" max="10" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18">
+    <row r="1" spans="1:10" ht="17.649999999999999">
       <c r="A1" s="17" t="s">
         <v>147</v>
       </c>
@@ -4417,7 +4431,7 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="30">
+    <row r="3" spans="1:10" ht="27.75">
       <c r="A3" s="2" t="s">
         <v>148</v>
       </c>
@@ -4449,7 +4463,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="99.75">
+    <row r="4" spans="1:10" ht="94.5">
       <c r="A4" s="4" t="s">
         <v>293</v>
       </c>
@@ -4483,7 +4497,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="85.5">
+    <row r="5" spans="1:10" ht="81">
       <c r="A5" s="4" t="s">
         <v>296</v>
       </c>
@@ -4517,7 +4531,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="114">
+    <row r="6" spans="1:10" ht="94.5">
       <c r="A6" s="4" t="s">
         <v>298</v>
       </c>
@@ -4551,7 +4565,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="128.25">
+    <row r="7" spans="1:10" ht="108">
       <c r="A7" s="4" t="s">
         <v>300</v>
       </c>
@@ -4585,7 +4599,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="57">
+    <row r="8" spans="1:10" ht="54">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="6"/>
@@ -4617,7 +4631,7 @@
       <c r="I9" s="12"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:10" ht="15">
+    <row r="10" spans="1:10" ht="13.9">
       <c r="A10" s="2" t="s">
         <v>155</v>
       </c>
@@ -4637,7 +4651,7 @@
       <c r="I10" s="12"/>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:10" ht="57">
+    <row r="11" spans="1:10" ht="40.5">
       <c r="A11" s="1" t="s">
         <v>156</v>
       </c>
@@ -4658,7 +4672,7 @@
       <c r="I11" s="12"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:10" ht="114">
+    <row r="12" spans="1:10" ht="108">
       <c r="A12" s="1" t="s">
         <v>159</v>
       </c>
@@ -4679,7 +4693,7 @@
       <c r="I12" s="12"/>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:10" ht="42.75">
+    <row r="13" spans="1:10" ht="40.5">
       <c r="A13" s="1" t="s">
         <v>161</v>
       </c>
@@ -4700,7 +4714,7 @@
       <c r="I13" s="12"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:10" ht="28.5">
+    <row r="14" spans="1:10" ht="27">
       <c r="A14" s="1" t="s">
         <v>164</v>
       </c>
@@ -5047,7 +5061,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="5" width="20" customWidth="1"/>
@@ -5056,7 +5070,7 @@
     <col min="8" max="10" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18">
+    <row r="1" spans="1:10" ht="17.649999999999999">
       <c r="A1" s="17" t="s">
         <v>166</v>
       </c>
@@ -5082,7 +5096,7 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="15">
+    <row r="3" spans="1:10" ht="13.9">
       <c r="A3" s="2" t="s">
         <v>155</v>
       </c>
@@ -5104,7 +5118,7 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="28.5">
+    <row r="4" spans="1:10" ht="27">
       <c r="A4" s="1" t="s">
         <v>141</v>
       </c>
@@ -5129,7 +5143,7 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="28.5">
+    <row r="5" spans="1:10" ht="27">
       <c r="A5" s="1" t="s">
         <v>168</v>
       </c>
@@ -5154,7 +5168,7 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="42.75">
+    <row r="6" spans="1:10" ht="40.5">
       <c r="A6" s="1" t="s">
         <v>170</v>
       </c>
@@ -5179,7 +5193,7 @@
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10" ht="28.5">
+    <row r="7" spans="1:10" ht="27">
       <c r="A7" s="1" t="s">
         <v>104</v>
       </c>
@@ -5204,7 +5218,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="42.75">
+    <row r="8" spans="1:10" ht="40.5">
       <c r="A8" s="1" t="s">
         <v>172</v>
       </c>
@@ -5229,7 +5243,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" ht="28.5">
+    <row r="9" spans="1:10" ht="27">
       <c r="A9" s="1" t="s">
         <v>105</v>
       </c>
@@ -5254,7 +5268,7 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:10" ht="28.5">
+    <row r="10" spans="1:10" ht="27">
       <c r="A10" s="1" t="s">
         <v>174</v>
       </c>
@@ -5279,7 +5293,7 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:10" ht="28.5">
+    <row r="11" spans="1:10" ht="27">
       <c r="A11" s="1" t="s">
         <v>106</v>
       </c>
@@ -5304,7 +5318,7 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:10" ht="28.5">
+    <row r="12" spans="1:10" ht="27">
       <c r="A12" s="1" t="s">
         <v>177</v>
       </c>
@@ -5329,7 +5343,7 @@
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:10" ht="28.5">
+    <row r="13" spans="1:10" ht="27">
       <c r="A13" s="1" t="s">
         <v>179</v>
       </c>
@@ -5692,7 +5706,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="5" width="20" customWidth="1"/>
@@ -5701,7 +5715,7 @@
     <col min="8" max="10" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18">
+    <row r="1" spans="1:10" ht="17.649999999999999">
       <c r="A1" s="17" t="s">
         <v>181</v>
       </c>
@@ -5727,7 +5741,7 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="30">
+    <row r="3" spans="1:10" ht="27.75">
       <c r="A3" s="2" t="s">
         <v>102</v>
       </c>
@@ -5753,7 +5767,7 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="42.75">
+    <row r="4" spans="1:10" ht="40.5">
       <c r="A4" s="1" t="s">
         <v>108</v>
       </c>
@@ -5784,7 +5798,7 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="42.75">
+    <row r="5" spans="1:10" ht="40.5">
       <c r="A5" s="1" t="s">
         <v>109</v>
       </c>
@@ -5815,7 +5829,7 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="42.75">
+    <row r="6" spans="1:10" ht="40.5">
       <c r="A6" s="1" t="s">
         <v>110</v>
       </c>
@@ -5858,7 +5872,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="15">
+    <row r="8" spans="1:10" ht="13.9">
       <c r="A8" s="2" t="s">
         <v>155</v>
       </c>
@@ -5878,7 +5892,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" ht="42.75">
+    <row r="9" spans="1:10" ht="40.5">
       <c r="A9" s="1" t="s">
         <v>191</v>
       </c>
@@ -5899,7 +5913,7 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:10" ht="28.5">
+    <row r="10" spans="1:10" ht="27">
       <c r="A10" s="1" t="s">
         <v>194</v>
       </c>
@@ -5920,7 +5934,7 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:10" ht="42.75">
+    <row r="11" spans="1:10" ht="40.5">
       <c r="A11" s="1" t="s">
         <v>197</v>
       </c>
@@ -5941,7 +5955,7 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:10" ht="42.75">
+    <row r="12" spans="1:10" ht="40.5">
       <c r="A12" s="1" t="s">
         <v>200</v>
       </c>
@@ -6350,7 +6364,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="5" width="20" customWidth="1"/>
@@ -6359,7 +6373,7 @@
     <col min="8" max="10" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18">
+    <row r="1" spans="1:10" ht="17.649999999999999">
       <c r="A1" s="17" t="s">
         <v>203</v>
       </c>
@@ -6385,7 +6399,7 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="30">
+    <row r="3" spans="1:10" ht="27.75">
       <c r="A3" s="2" t="s">
         <v>102</v>
       </c>
@@ -6411,7 +6425,7 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="28.5">
+    <row r="4" spans="1:10" ht="27">
       <c r="A4" s="1" t="s">
         <v>108</v>
       </c>
@@ -6442,7 +6456,7 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="28.5">
+    <row r="5" spans="1:10" ht="27">
       <c r="A5" s="1" t="s">
         <v>109</v>
       </c>
@@ -6473,7 +6487,7 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="42.75">
+    <row r="6" spans="1:10" ht="40.5">
       <c r="A6" s="1" t="s">
         <v>110</v>
       </c>
@@ -6516,7 +6530,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="15">
+    <row r="8" spans="1:10" ht="13.9">
       <c r="A8" s="2" t="s">
         <v>155</v>
       </c>
@@ -6536,7 +6550,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" ht="28.5">
+    <row r="9" spans="1:10" ht="27">
       <c r="A9" s="1" t="s">
         <v>209</v>
       </c>
@@ -6559,7 +6573,7 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:10" ht="28.5">
+    <row r="10" spans="1:10" ht="27">
       <c r="A10" s="1" t="s">
         <v>204</v>
       </c>
@@ -6953,7 +6967,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="5" width="20" customWidth="1"/>
@@ -6962,7 +6976,7 @@
     <col min="8" max="10" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18">
+    <row r="1" spans="1:10" ht="17.649999999999999">
       <c r="A1" s="17" t="s">
         <v>210</v>
       </c>
@@ -6988,7 +7002,7 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="30">
+    <row r="3" spans="1:10" ht="13.9">
       <c r="A3" s="2" t="s">
         <v>61</v>
       </c>
@@ -7016,7 +7030,7 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="85.5">
+    <row r="4" spans="1:10" ht="81">
       <c r="A4" s="1" t="s">
         <v>212</v>
       </c>
@@ -7044,7 +7058,7 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="28.5">
+    <row r="5" spans="1:10" ht="27">
       <c r="A5" s="1" t="s">
         <v>215</v>
       </c>
@@ -7072,7 +7086,7 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="28.5">
+    <row r="6" spans="1:10" ht="27">
       <c r="A6" s="1" t="s">
         <v>217</v>
       </c>
@@ -7131,7 +7145,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="28.5">
+    <row r="8" spans="1:10" ht="27">
       <c r="A8" s="1" t="s">
         <v>222</v>
       </c>
@@ -7162,7 +7176,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" ht="28.5">
+    <row r="9" spans="1:10" ht="27">
       <c r="A9" s="1" t="s">
         <v>224</v>
       </c>
@@ -7576,7 +7590,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="5" width="20" customWidth="1"/>
@@ -7585,7 +7599,7 @@
     <col min="8" max="10" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18">
+    <row r="1" spans="1:10" ht="17.649999999999999">
       <c r="A1" s="17" t="s">
         <v>226</v>
       </c>
@@ -7611,7 +7625,7 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="15">
+    <row r="3" spans="1:10" ht="13.9">
       <c r="A3" s="2" t="s">
         <v>227</v>
       </c>
@@ -7631,7 +7645,7 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="28.5">
+    <row r="4" spans="1:10" ht="27">
       <c r="A4" s="1" t="s">
         <v>141</v>
       </c>
@@ -7652,7 +7666,7 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="28.5">
+    <row r="5" spans="1:10" ht="27">
       <c r="A5" s="1" t="s">
         <v>144</v>
       </c>
@@ -7673,7 +7687,7 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="57">
+    <row r="6" spans="1:10" ht="54">
       <c r="A6" s="1" t="s">
         <v>230</v>
       </c>
@@ -7694,7 +7708,7 @@
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10" ht="28.5">
+    <row r="7" spans="1:10" ht="27">
       <c r="A7" s="1" t="s">
         <v>233</v>
       </c>
@@ -7715,7 +7729,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="28.5">
+    <row r="8" spans="1:10" ht="27">
       <c r="A8" s="1" t="s">
         <v>236</v>
       </c>
@@ -7736,7 +7750,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" ht="28.5">
+    <row r="9" spans="1:10" ht="27">
       <c r="A9" s="1" t="s">
         <v>238</v>
       </c>
@@ -7757,7 +7771,7 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:10" ht="42.75">
+    <row r="10" spans="1:10" ht="40.5">
       <c r="A10" s="1" t="s">
         <v>240</v>
       </c>
@@ -7778,7 +7792,7 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:10" ht="42.75">
+    <row r="11" spans="1:10" ht="40.5">
       <c r="A11" s="1" t="s">
         <v>242</v>
       </c>
@@ -7799,7 +7813,7 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:10" ht="42.75">
+    <row r="12" spans="1:10" ht="40.5">
       <c r="A12" s="1" t="s">
         <v>244</v>
       </c>
@@ -7832,7 +7846,7 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:10" ht="30">
+    <row r="14" spans="1:10" ht="27.75">
       <c r="A14" s="2" t="s">
         <v>246</v>
       </c>
